--- a/excel files/Vorlage_IPC1_Vorschneiden.xlsx
+++ b/excel files/Vorlage_IPC1_Vorschneiden.xlsx
@@ -5,13 +5,13 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Produktion\1_Artikel\1_Marke\31962\IPC_Etiketten_Packliste\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\questalpha.intern\files\daten\Produktion\1_Artikel\1_Marke\31963\IPC_Etiketten_Packliste\LOT 265191\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8289A5-4554-4AD3-B689-163FF36AFD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4F5480-96BB-44CA-9127-D1996A160D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="yrNcbWYE1dPbAoJloAQwS0/5rxTf+qz2pbLvi7BpPdYxtEEZItxMK1PreEHWIukmvZW4pBFHpPX6y31D3p/wDg==" workbookSaltValue="67AVBMQ8KZDQzYjHdlNnbw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Rollen Nr.</t>
   </si>
@@ -44,9 +55,6 @@
   </si>
   <si>
     <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
   </si>
   <si>
     <t>Mittelwert</t>
@@ -86,12 +94,6 @@
     </r>
   </si>
   <si>
-    <t>REF 31962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sugi Instrument Wipe, 80x80mm, none-sterile, 250 pcs. </t>
-  </si>
-  <si>
     <t>Arbeitsmaßstab:</t>
   </si>
   <si>
@@ -99,44 +101,16 @@
 LOT 50814.D</t>
   </si>
   <si>
+    <t>Bahn Soll: 180 - 190 mm</t>
+  </si>
+  <si>
     <t>30.09.2024 S. Rüther</t>
   </si>
   <si>
-    <t>Breite der Bahn Bahn 
-Soll: 180 - 190 mm</t>
+    <t>REF 31963</t>
   </si>
   <si>
-    <t>50-2  20.03.2026 Walter</t>
-  </si>
-  <si>
-    <t>188B</t>
-  </si>
-  <si>
-    <t>ja</t>
-  </si>
-  <si>
-    <t>20.03.2026 Walter</t>
-  </si>
-  <si>
-    <t>186B</t>
-  </si>
-  <si>
-    <t>183B</t>
-  </si>
-  <si>
-    <t>23.03.2026 Walter</t>
-  </si>
-  <si>
-    <t>185B</t>
-  </si>
-  <si>
-    <t>184B</t>
-  </si>
-  <si>
-    <t>182B</t>
-  </si>
-  <si>
-    <t>187B</t>
+    <t xml:space="preserve">Sugi Instrument Wipe Xtra, 80x80mm, none-sterile, 250 pcs. </t>
   </si>
 </sst>
 </file>
@@ -146,7 +120,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,12 +150,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -194,6 +162,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri   "/>
     </font>
     <font>
       <sz val="8"/>
@@ -216,7 +189,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -488,23 +461,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -512,7 +517,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -546,9 +551,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -565,10 +567,38 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -581,7 +611,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -675,10 +705,10 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="A2" t="str">
-            <v>2031-02-28</v>
+            <v>2031-03-31</v>
           </cell>
           <cell r="B2">
-            <v>265321</v>
+            <v>265191</v>
           </cell>
         </row>
       </sheetData>
@@ -956,624 +986,511 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" customWidth="1"/>
-    <col min="6" max="6" width="29.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="11"/>
+    </row>
+    <row r="4" spans="1:7" ht="18.75">
+      <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="33">
         <f>[1]Tabelle1!$B$2</f>
-        <v>265321</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>17</v>
-      </c>
+        <v>265191</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="30"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:7" ht="18.75">
+      <c r="A5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="str">
+      <c r="B5" s="14" t="str">
         <f>[1]Tabelle1!$A$2</f>
-        <v>2031-02-28</v>
-      </c>
-      <c r="C5" s="9"/>
+        <v>2031-03-31</v>
+      </c>
+      <c r="C5" s="15"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="11"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A7" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="48" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="30" t="s">
+      <c r="D8" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="45"/>
+      <c r="F8" s="46" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="18">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <v>2</v>
+      </c>
+      <c r="F9" s="47"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="22">
+        <f>MIN(D13:D56)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="33" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="12">
-        <v>1</v>
-      </c>
-      <c r="E9" s="13">
-        <v>2</v>
-      </c>
-      <c r="F9" s="34"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="16">
-        <f>MIN(D13:D56)</f>
-        <v>182</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="E10" s="22">
         <f>MIN(E13:E56)</f>
-        <v>182</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="20">
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="37" t="e">
         <f>SUBTOTAL(1,D13:D56)</f>
-        <v>182.375</v>
-      </c>
-      <c r="E11" s="20">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E11" s="37" t="e">
         <f t="shared" ref="E11" si="0">SUBTOTAL(1,E13:E56)</f>
-        <v>182.25</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="22">
-        <f>MAX(D13:D56)</f>
-        <v>183</v>
-      </c>
-      <c r="E12" s="22">
-        <f>MAX(E13:E56)</f>
-        <v>183</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>1242694</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="4">
-        <v>182</v>
-      </c>
-      <c r="E13" s="4">
-        <v>182</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>1242694</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="4">
-        <v>182</v>
-      </c>
-      <c r="E14" s="4">
-        <v>182</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <v>1242694</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4">
-        <v>183</v>
-      </c>
-      <c r="E15" s="4">
-        <v>183</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>1242694</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="4">
-        <v>182</v>
-      </c>
-      <c r="E16" s="4">
-        <v>182</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
-        <v>1242694</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="4">
-        <v>183</v>
-      </c>
-      <c r="E17" s="4">
-        <v>182</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>1242694</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="4">
-        <v>182</v>
-      </c>
-      <c r="E18" s="4">
-        <v>182</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
-        <v>1242694</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="4">
-        <v>183</v>
-      </c>
-      <c r="E19" s="4">
-        <v>182</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <v>124294</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="4">
-        <v>182</v>
-      </c>
-      <c r="E20" s="4">
-        <v>183</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="3"/>
-    </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="3"/>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="3"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="3"/>
-    </row>
-    <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="3"/>
-    </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="2"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="3"/>
-    </row>
-    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="2"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="3"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="3"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A13" s="35"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A14" s="35"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A15" s="35"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A16" s="35"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="35"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="36"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="36"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="34"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="34"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="34"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="34"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="34"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="34"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="34"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="34"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="34"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="34"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="34"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="40"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="8"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="8"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="8"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="8"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="8"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="8"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="8"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="8"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="39"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="8"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="8"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="8"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="8"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="8"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="8"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="8"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="8"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="8"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="8"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="8"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="8"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="8"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="7"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="8"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="7"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="8"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="7"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="10"/>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BJthn0xbHwHSzaxlf9mkQSYYrRuFzEgtmjmD0ZX+bolUrj71DAfi5R05Mo0DtdBpiX/5yYRNicGxLcv71aAHmA==" saltValue="5fFqULegbI4+3DlDfSJxVg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="5">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
@@ -1590,12 +1507,12 @@
       <formula>170</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12:E56">
+  <conditionalFormatting sqref="D12:E38 D40:E56">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>190</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13:E56">
+  <conditionalFormatting sqref="D13:E38 D40:E56">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -1604,6 +1521,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="81" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="84" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>